--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCP.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,11 +421,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0 | F. Amarante (-6.2 net)</t>
+          <t>Liam Reilly (19.5 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F. Amarante (24.4 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Liam Reilly (50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F. Amarante | Liam Reilly (3.1 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0 | F. Amarante | G. Kalscheur (-2.3 net)</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F. Amarante | J. Fernandes | Liam Reilly (4.5 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +548,461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>44.7%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>44.7%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>62.1%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>45.2%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, shooter, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>47.5%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,7 +1051,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -657,26 +1130,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0 | F. Amarante</t>
+          <t>F. Amarante | Liam Reilly</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>25.6</v>
+        <v>38.8</v>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>79.3</v>
       </c>
       <c r="I2" t="n">
-        <v>84.2</v>
+        <v>76.3</v>
       </c>
       <c r="J2" t="n">
-        <v>-6.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1170,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0 | G. Kalscheur</t>
+          <t>D. Ventura | G. Kalscheur</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3</v>
+        <v>25.3</v>
       </c>
       <c r="H3" t="n">
-        <v>71.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.3</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="4">
@@ -737,26 +1210,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>G. Kalscheur | J. Embalo</t>
+          <t>D. Ventura | G. Kalscheur</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>15.9</v>
+        <v>25.3</v>
       </c>
       <c r="H4" t="n">
-        <v>70.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>72.8</v>
+        <v>53.8</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.5</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1250,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0 | F. Amarante | G. Kalscheur</t>
+          <t>F. Amarante | J. Fernandes | Liam Reilly</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>17.3</v>
+        <v>26.6</v>
       </c>
       <c r="H5" t="n">
-        <v>71.8</v>
+        <v>79.7</v>
       </c>
       <c r="I5" t="n">
-        <v>74.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -817,26 +1290,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0 | F. Amarante | G. Kalscheur</t>
+          <t>A. Cruz | D. Ventura | J. Davis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="H6" t="n">
-        <v>71.8</v>
+        <v>88.7</v>
       </c>
       <c r="I6" t="n">
-        <v>74.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1330,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0 | F. Amarante | G. Kalscheur</t>
+          <t>F. Amarante | G. Kalscheur | Liam Reilly</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>17.3</v>
+        <v>19.6</v>
       </c>
       <c r="H7" t="n">
-        <v>71.8</v>
+        <v>67.2</v>
       </c>
       <c r="I7" t="n">
-        <v>74.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.3</v>
+        <v>-6.1</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCP.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Amarante (24.4 mpg)</t>
+          <t>F. Amarante (25.9 mpg)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F. Amarante | Liam Reilly (3.1 net)</t>
+          <t>F. Amarante | Liam Reilly (1.8 net)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -698,65 +698,69 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>48.7</v>
+        <v>77.8</v>
       </c>
       <c r="G2" t="n">
-        <v>24.4</v>
+        <v>25.9</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>11.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="T2" t="n">
-        <v>-23.4</v>
+        <v>-7.2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes</t>
+          <t>high-minutes, shooter</t>
         </is>
       </c>
     </row>
@@ -768,74 +772,78 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>48.6</v>
+        <v>70.3</v>
       </c>
       <c r="G3" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="H3" t="n">
-        <v>19.5</v>
+        <v>7.7</v>
       </c>
       <c r="I3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="T3" t="n">
-        <v>-14.9</v>
+        <v>4.8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -852,43 +860,43 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -898,23 +906,23 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>20.8</v>
+        <v>6.2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, shooter, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -926,83 +934,482 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>64.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>58.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>62.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>47.5%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
+      <c r="F8" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>rotation</t>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>57.4%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Fernandes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Cruz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>50.5%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U5"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1134,22 +1541,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>38.8</v>
+        <v>43.6</v>
       </c>
       <c r="H2" t="n">
-        <v>79.3</v>
+        <v>76.2</v>
       </c>
       <c r="I2" t="n">
-        <v>76.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
@@ -1170,26 +1577,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D. Ventura | G. Kalscheur</t>
+          <t>F. Amarante | Liam Reilly</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>25.3</v>
+        <v>43.6</v>
       </c>
       <c r="H3" t="n">
-        <v>77.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I3" t="n">
-        <v>53.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>23.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -1210,26 +1617,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D. Ventura | G. Kalscheur</t>
+          <t>F. Amarante | Liam Reilly</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>25.3</v>
+        <v>43.6</v>
       </c>
       <c r="H4" t="n">
-        <v>77.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I4" t="n">
-        <v>53.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>23.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -1290,26 +1697,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Cruz | D. Ventura | J. Davis</t>
+          <t>D. Ventura | J. Davis | J. Embalo</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>16.7</v>
+        <v>24.7</v>
       </c>
       <c r="H6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="I6" t="n">
-        <v>79.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="J6" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1330,26 +1737,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>F. Amarante | G. Kalscheur | Liam Reilly</t>
+          <t>D. Ventura | J. Davis | J. Embalo</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>19.6</v>
+        <v>24.7</v>
       </c>
       <c r="H7" t="n">
-        <v>67.2</v>
+        <v>76.2</v>
       </c>
       <c r="I7" t="n">
-        <v>73.3</v>
+        <v>66.5</v>
       </c>
       <c r="J7" t="n">
-        <v>-6.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCP.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Liam Reilly (19.5 ppg)</t>
+          <t>Liam Reilly (15.2 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Amarante (25.9 mpg)</t>
+          <t>F. Amarante (26.1 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liam Reilly (50.0%)</t>
+          <t>A. Cruz (40.0%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F. Amarante | Liam Reilly (1.8 net)</t>
+          <t>F. Amarante | Liam Reilly (-4.2 net)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F. Amarante | J. Fernandes | Liam Reilly (4.5 net)</t>
+          <t>D. Ventura | F. Amarante | J. Davis (-8.3 net)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="41" customWidth="1" min="21" max="21"/>
+    <col width="39" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,69 +698,69 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>77.8</v>
+        <v>104.2</v>
       </c>
       <c r="G2" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="H2" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.2</v>
+        <v>-10.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes, shooter</t>
+          <t>high-minutes</t>
         </is>
       </c>
     </row>
@@ -781,28 +781,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>70.3</v>
+        <v>101.7</v>
       </c>
       <c r="G3" t="n">
-        <v>23.4</v>
+        <v>25.4</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -812,38 +812,38 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>4.8</v>
+        <v>10.3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>rotation</t>
+          <t>high-minutes, efficient, impact</t>
         </is>
       </c>
     </row>
@@ -855,74 +855,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>67.2</v>
+        <v>96.2</v>
       </c>
       <c r="G4" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>10.7</v>
+        <v>15.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>-0.8</v>
       </c>
       <c r="T4" t="n">
-        <v>6.2</v>
+        <v>-10.6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>high-minutes, primary-scorer, shooter</t>
         </is>
       </c>
     </row>
@@ -934,74 +934,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Davis</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
-        <v>57.7</v>
+        <v>92.5</v>
       </c>
       <c r="G5" t="n">
-        <v>19.2</v>
+        <v>23.1</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>54.5%</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>-5</v>
+        <v>13.3</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>efficient</t>
+          <t>shooter, impact</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,65 +1022,65 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>57.7</v>
+        <v>78.7</v>
       </c>
       <c r="G6" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="H6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>58.6%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-5</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>-32.9</v>
+        <v>-1.4</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>rotation</t>
+          <t>efficient</t>
         </is>
       </c>
     </row>
@@ -1092,74 +1092,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>-4</v>
       </c>
       <c r="T7" t="n">
-        <v>-14.9</v>
+        <v>-22.4</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1171,74 +1175,78 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>J. Fernandes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>48.5</v>
+        <v>54.5</v>
       </c>
       <c r="G8" t="n">
-        <v>16.2</v>
+        <v>13.6</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T8" t="n">
         <v>0.7</v>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>58.3%</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>57.4%</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>22.9</v>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1250,47 +1258,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1300,24 +1304,24 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>5.6</v>
+        <v>22.2</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1458,7 +1462,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1541,22 +1545,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>43.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>76.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>74.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="3">
@@ -1577,26 +1581,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>F. Amarante | Liam Reilly</t>
+          <t>D. Ventura | G. Kalscheur</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>43.6</v>
+        <v>55.2</v>
       </c>
       <c r="H3" t="n">
-        <v>76.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="4">
@@ -1617,26 +1621,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F. Amarante | Liam Reilly</t>
+          <t>D. Ventura | G. Kalscheur</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>43.6</v>
+        <v>55.2</v>
       </c>
       <c r="H4" t="n">
-        <v>76.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>74.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="5">
@@ -1657,26 +1661,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F. Amarante | J. Fernandes | Liam Reilly</t>
+          <t>D. Ventura | F. Amarante | J. Davis</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>26.6</v>
+        <v>33.8</v>
       </c>
       <c r="H5" t="n">
-        <v>79.7</v>
+        <v>79.3</v>
       </c>
       <c r="I5" t="n">
-        <v>75.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1697,26 +1701,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D. Ventura | J. Davis | J. Embalo</t>
+          <t>D. Ventura | G. Kalscheur | J. Davis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>24.7</v>
+        <v>33.5</v>
       </c>
       <c r="H6" t="n">
-        <v>76.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>66.5</v>
+        <v>62.1</v>
       </c>
       <c r="J6" t="n">
-        <v>9.699999999999999</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="7">
@@ -1741,22 +1745,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>24.7</v>
+        <v>30.7</v>
       </c>
       <c r="H7" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="I7" t="n">
-        <v>66.5</v>
+        <v>60</v>
       </c>
       <c r="J7" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
     </row>
   </sheetData>
